--- a/output/pdf_financials_xlsx/RGR.xlsx
+++ b/output/pdf_financials_xlsx/RGR.xlsx
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.555955</v>
       </c>
     </row>
     <row r="93">
@@ -2856,7 +2856,11 @@
           <t>Share based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RGR.xlsx
+++ b/output/pdf_financials_xlsx/RGR.xlsx
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.73161</v>
       </c>
     </row>
     <row r="35">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.73161</v>
       </c>
     </row>
     <row r="37">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.607586</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/pdf_financials_xlsx/RGR.xlsx
+++ b/output/pdf_financials_xlsx/RGR.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.100303</v>
+        <v>0.106553</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.242369</v>
+        <v>0.248619</v>
       </c>
     </row>
     <row r="11">
@@ -3884,7 +3884,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
